--- a/Outputs/Recycling_Plot_Data/Repeal/07_Exported_Minerals_data_Repeal.xlsx
+++ b/Outputs/Recycling_Plot_Data/Repeal/07_Exported_Minerals_data_Repeal.xlsx
@@ -1414,7 +1414,7 @@
         </is>
       </c>
       <c r="E38">
-        <v>1.621038845891725</v>
+        <v>1.491155889210084</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="E39">
-        <v>8.846284045881935</v>
+        <v>8.177182433320519</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="E40">
-        <v>17.96853918228675</v>
+        <v>16.5968784602992</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         </is>
       </c>
       <c r="E41">
-        <v>1.695248305200431</v>
+        <v>1.565052611400262</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="E42">
-        <v>0.7402973934381928</v>
+        <v>0.6815561157268297</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         </is>
       </c>
       <c r="E43">
-        <v>8.326884144228904</v>
+        <v>7.661620188609055</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         </is>
       </c>
       <c r="E44">
-        <v>1.603968191839575</v>
+        <v>1.477321601422331</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="E45">
-        <v>9.081702922088322</v>
+        <v>8.410942051251839</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="E46">
-        <v>18.33275676975509</v>
+        <v>16.9644643888611</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         </is>
       </c>
       <c r="E47">
-        <v>1.723102996199265</v>
+        <v>1.593607735690206</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="E48">
-        <v>0.7270831903222869</v>
+        <v>0.6701674874554978</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -1722,7 +1722,7 @@
         </is>
       </c>
       <c r="E49">
-        <v>8.234279550594435</v>
+        <v>7.58601281287144</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         </is>
       </c>
       <c r="E50">
-        <v>0.9287835023992118</v>
+        <v>0.7517721959370182</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="E51">
-        <v>4.665492212472641</v>
+        <v>3.792042922125011</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="E52">
-        <v>9.622018677228617</v>
+        <v>7.815429457741618</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="E53">
-        <v>0.9159487277251581</v>
+        <v>0.7436428768585766</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="E54">
-        <v>0.4226291475332924</v>
+        <v>0.3424050373991251</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         </is>
       </c>
       <c r="E55">
-        <v>4.796756233280717</v>
+        <v>3.884010772471068</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         </is>
       </c>
       <c r="E56">
-        <v>0.9448616775988176</v>
+        <v>0.7728162378740031</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         </is>
       </c>
       <c r="E57">
-        <v>4.91889168395083</v>
+        <v>4.042908872433668</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         </is>
       </c>
       <c r="E58">
-        <v>10.07966808318977</v>
+        <v>8.278242590703227</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -2002,7 +2002,7 @@
         </is>
       </c>
       <c r="E59">
-        <v>0.9558528158627159</v>
+        <v>0.7846213315858969</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="E60">
-        <v>0.426901111598417</v>
+        <v>0.3494580843147592</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
         </is>
       </c>
       <c r="E61">
-        <v>4.878124146682993</v>
+        <v>3.991404250430532</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="E62">
-        <v>4.173961609454278</v>
+        <v>3.983200694954025</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="E63">
-        <v>22.69648246843067</v>
+        <v>21.77241210674668</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -2142,7 +2142,7 @@
         </is>
       </c>
       <c r="E64">
-        <v>46.23825725045319</v>
+        <v>44.3212821991045</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         </is>
       </c>
       <c r="E65">
-        <v>4.364276819369265</v>
+        <v>4.181096443437727</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="E66">
-        <v>1.953451142962293</v>
+        <v>1.866692420253262</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="E67">
-        <v>21.71121364664457</v>
+        <v>20.72977022540386</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         </is>
       </c>
       <c r="E68">
-        <v>4.063004097912888</v>
+        <v>3.876542605731666</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         </is>
       </c>
       <c r="E69">
-        <v>23.10638341581294</v>
+        <v>22.17972817218854</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -2310,7 +2310,7 @@
         </is>
       </c>
       <c r="E70">
-        <v>46.71808297098651</v>
+        <v>44.80505258013775</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="E71">
-        <v>4.389439094858427</v>
+        <v>4.207146787297889</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         </is>
       </c>
       <c r="E72">
-        <v>1.886100220591006</v>
+        <v>1.801802621340951</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         </is>
       </c>
       <c r="E73">
-        <v>21.12460999581337</v>
+        <v>20.16602885244965</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         </is>
       </c>
       <c r="E74">
-        <v>4.239014748725117</v>
+        <v>3.691566450351717</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
         </is>
       </c>
       <c r="E75">
-        <v>21.16223160954732</v>
+        <v>18.59463119529516</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         </is>
       </c>
       <c r="E76">
-        <v>43.72431787567054</v>
+        <v>38.36542379280313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         </is>
       </c>
       <c r="E77">
-        <v>4.164692242294858</v>
+        <v>3.650746363383941</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -2534,7 +2534,7 @@
         </is>
       </c>
       <c r="E78">
-        <v>1.970137268868345</v>
+        <v>1.721211341453823</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         </is>
       </c>
       <c r="E79">
-        <v>21.95693350179888</v>
+        <v>19.13954165343192</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -2590,7 +2590,7 @@
         </is>
       </c>
       <c r="E80">
-        <v>4.153310828264031</v>
+        <v>3.618879368025774</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         </is>
       </c>
       <c r="E81">
-        <v>21.59726685445179</v>
+        <v>19.02356862998378</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         </is>
       </c>
       <c r="E82">
-        <v>44.29484979226947</v>
+        <v>38.95058306933614</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -2674,7 +2674,7 @@
         </is>
       </c>
       <c r="E83">
-        <v>4.200646200425836</v>
+        <v>3.689608329235606</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -2702,7 +2702,7 @@
         </is>
       </c>
       <c r="E84">
-        <v>1.915984823532559</v>
+        <v>1.674418084728292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         </is>
       </c>
       <c r="E85">
-        <v>21.50332911223493</v>
+        <v>18.75457281218438</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -2758,7 +2758,7 @@
         </is>
       </c>
       <c r="E86">
-        <v>7.938499761460208</v>
+        <v>7.368933019916618</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         </is>
       </c>
       <c r="E87">
-        <v>42.68378730931864</v>
+        <v>40.0577728312679</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
         </is>
       </c>
       <c r="E88">
-        <v>87.17451713802727</v>
+        <v>81.67962180698206</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         </is>
       </c>
       <c r="E89">
-        <v>8.237136615617054</v>
+        <v>7.709168482393109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         </is>
       </c>
       <c r="E90">
-        <v>3.792473157507654</v>
+        <v>3.534407905277781</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         </is>
       </c>
       <c r="E91">
-        <v>41.39371806373695</v>
+        <v>38.47198518596438</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="E92">
-        <v>7.662352471298963</v>
+        <v>7.103223907590359</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="E93">
-        <v>43.36342217041055</v>
+        <v>40.73192449037526</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="E94">
-        <v>87.79120058263105</v>
+        <v>82.30734122350779</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
         </is>
       </c>
       <c r="E95">
-        <v>8.252015557185757</v>
+        <v>7.726325130714058</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         </is>
       </c>
       <c r="E96">
-        <v>3.629574198611499</v>
+        <v>3.377534073358199</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="E97">
-        <v>39.92900763477712</v>
+        <v>37.0630627948484</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -3094,7 +3094,7 @@
         </is>
       </c>
       <c r="E98">
-        <v>6.822930627374955</v>
+        <v>6.176924616544865</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -3122,7 +3122,7 @@
         </is>
       </c>
       <c r="E99">
-        <v>34.64585200690864</v>
+        <v>31.66438641018155</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="E100">
-        <v>71.38356948284968</v>
+        <v>65.14454812490507</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="E101">
-        <v>6.785947141959681</v>
+        <v>6.186550760292366</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -3206,7 +3206,7 @@
         </is>
       </c>
       <c r="E102">
-        <v>3.27982655956845</v>
+        <v>2.983111381464903</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         </is>
       </c>
       <c r="E103">
-        <v>35.34367087584283</v>
+        <v>32.02736636792461</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -3262,7 +3262,7 @@
         </is>
       </c>
       <c r="E104">
-        <v>6.596930545805751</v>
+        <v>5.967281801111032</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         </is>
       </c>
       <c r="E105">
-        <v>35.36751565079175</v>
+        <v>32.37814203729753</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="E106">
-        <v>72.17069786555048</v>
+        <v>65.94970544501219</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -3346,7 +3346,7 @@
         </is>
       </c>
       <c r="E107">
-        <v>6.821489869823826</v>
+        <v>6.225718827143978</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         </is>
       </c>
       <c r="E108">
-        <v>3.145283428758717</v>
+        <v>2.857907916935232</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
         </is>
       </c>
       <c r="E109">
-        <v>34.15159386038609</v>
+        <v>30.92166489053743</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -3430,7 +3430,7 @@
         </is>
       </c>
       <c r="E110">
-        <v>11.07578725349774</v>
+        <v>10.40069267703987</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="E111">
-        <v>60.36355431269429</v>
+        <v>57.31112968118246</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -3486,7 +3486,7 @@
         </is>
       </c>
       <c r="E112">
-        <v>123.0393042965212</v>
+        <v>116.6307881761134</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         </is>
       </c>
       <c r="E113">
-        <v>11.6084395215912</v>
+        <v>10.99134044555579</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="E114">
-        <v>5.474406261255533</v>
+        <v>5.167301131265794</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="E115">
-        <v>57.78204722549813</v>
+        <v>54.3263785124856</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -3598,7 +3598,7 @@
         </is>
       </c>
       <c r="E116">
-        <v>10.55133151260807</v>
+        <v>9.888997152669941</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         </is>
       </c>
       <c r="E117">
-        <v>61.47072886099222</v>
+        <v>58.41124735735794</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -3654,7 +3654,7 @@
         </is>
       </c>
       <c r="E118">
-        <v>123.8996274565559</v>
+        <v>117.5040901096912</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         </is>
       </c>
       <c r="E119">
-        <v>11.61099650353584</v>
+        <v>10.99664007916058</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="E120">
-        <v>5.168524594294007</v>
+        <v>4.868859867790918</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
         </is>
       </c>
       <c r="E121">
-        <v>54.99846834372036</v>
+        <v>51.61119216943283</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         </is>
       </c>
       <c r="E122">
-        <v>9.341350724569667</v>
+        <v>8.65867176479518</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         </is>
       </c>
       <c r="E123">
-        <v>48.18880026951701</v>
+        <v>45.07711497471335</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
         </is>
       </c>
       <c r="E124">
-        <v>99.03597825979325</v>
+        <v>92.51078411389838</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -3850,7 +3850,7 @@
         </is>
       </c>
       <c r="E125">
-        <v>9.397523270224543</v>
+        <v>8.76978403966606</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         </is>
       </c>
       <c r="E126">
-        <v>4.653308742572172</v>
+        <v>4.337292436956432</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -3906,7 +3906,7 @@
         </is>
       </c>
       <c r="E127">
-        <v>48.38909691778851</v>
+        <v>44.89060899897866</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         </is>
       </c>
       <c r="E128">
-        <v>8.881609286533871</v>
+        <v>8.218514348555649</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         </is>
       </c>
       <c r="E129">
-        <v>49.36988970649051</v>
+        <v>46.24834754221251</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         </is>
       </c>
       <c r="E130">
-        <v>100.154286099019</v>
+        <v>93.65005440279393</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         </is>
       </c>
       <c r="E131">
-        <v>9.429936676682239</v>
+        <v>8.806486120324234</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="E132">
-        <v>4.385410741968303</v>
+        <v>4.080683325323103</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -4074,7 +4074,7 @@
         </is>
       </c>
       <c r="E133">
-        <v>45.96894064226931</v>
+        <v>42.57391425583553</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         </is>
       </c>
       <c r="E134">
-        <v>14.42912604986454</v>
+        <v>13.71247954578039</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         </is>
       </c>
       <c r="E135">
-        <v>79.43492527807791</v>
+        <v>76.24405201892044</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         </is>
       </c>
       <c r="E136">
-        <v>161.6970086889478</v>
+        <v>154.9794477472307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         </is>
       </c>
       <c r="E137">
-        <v>15.23802576062458</v>
+        <v>14.59004273708069</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         </is>
       </c>
       <c r="E138">
-        <v>7.386301476991695</v>
+        <v>7.059320947975881</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         </is>
       </c>
       <c r="E139">
-        <v>75.3227987940507</v>
+        <v>71.65934079848861</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -4270,7 +4270,7 @@
         </is>
       </c>
       <c r="E140">
-        <v>13.49817903494089</v>
+        <v>12.79634770663263</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -4298,7 +4298,7 @@
         </is>
       </c>
       <c r="E141">
-        <v>81.2241987850731</v>
+        <v>78.02454961602946</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         </is>
       </c>
       <c r="E142">
-        <v>162.9276666485724</v>
+        <v>156.2242612199022</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         </is>
       </c>
       <c r="E143">
-        <v>15.2180716453686</v>
+        <v>14.57319782721259</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         </is>
       </c>
       <c r="E144">
-        <v>6.846963561725103</v>
+        <v>6.528700181323566</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="E145">
-        <v>70.38407746604138</v>
+        <v>66.80018174111834</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         </is>
       </c>
       <c r="E146">
-        <v>11.80208053590986</v>
+        <v>11.1636353123925</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="E147">
-        <v>61.71200791732984</v>
+        <v>58.8318857765552</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -4494,7 +4494,7 @@
         </is>
       </c>
       <c r="E148">
-        <v>126.6087019592502</v>
+        <v>120.5571846539263</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -4522,7 +4522,7 @@
         </is>
       </c>
       <c r="E149">
-        <v>11.99504582389191</v>
+        <v>11.41221517389608</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
         </is>
       </c>
       <c r="E150">
-        <v>6.09489701144375</v>
+        <v>5.797539901955929</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -4578,7 +4578,7 @@
         </is>
       </c>
       <c r="E151">
-        <v>61.25299550678164</v>
+        <v>57.98251032717719</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         </is>
       </c>
       <c r="E152">
-        <v>10.98348706009233</v>
+        <v>10.36605653152464</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -4634,7 +4634,7 @@
         </is>
       </c>
       <c r="E153">
-        <v>63.56754115314875</v>
+        <v>60.67629241359634</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         </is>
       </c>
       <c r="E154">
-        <v>128.1793866078497</v>
+        <v>122.1495919701122</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         </is>
       </c>
       <c r="E155">
-        <v>12.01797768247943</v>
+        <v>11.43968632311515</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -4718,7 +4718,7 @@
         </is>
       </c>
       <c r="E156">
-        <v>5.622002380809509</v>
+        <v>5.336892074674136</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         </is>
       </c>
       <c r="E157">
-        <v>56.93774339660488</v>
+        <v>53.77863369058255</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         </is>
       </c>
       <c r="E158">
-        <v>18.04787126143014</v>
+        <v>17.37471050241424</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         </is>
       </c>
       <c r="E159">
-        <v>99.91602651244985</v>
+        <v>96.95524522988747</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         </is>
       </c>
       <c r="E160">
-        <v>203.3453435067856</v>
+        <v>197.0973524056621</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
         </is>
       </c>
       <c r="E161">
-        <v>19.14962551578086</v>
+        <v>18.54609672869125</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -4886,7 +4886,7 @@
         </is>
       </c>
       <c r="E162">
-        <v>9.560014236907325</v>
+        <v>9.25210252395941</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         </is>
       </c>
       <c r="E163">
-        <v>94.46167131802379</v>
+        <v>91.02141338720885</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         </is>
       </c>
       <c r="E164">
-        <v>16.50056447161903</v>
+        <v>15.84300091656862</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="E165">
-        <v>102.7180126867187</v>
+        <v>99.74718927701346</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -4998,7 +4998,7 @@
         </is>
       </c>
       <c r="E166">
-        <v>205.0949814312774</v>
+        <v>198.8606794936726</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         </is>
       </c>
       <c r="E167">
-        <v>19.09195199332184</v>
+        <v>18.49159748152923</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         </is>
       </c>
       <c r="E168">
-        <v>8.665780128404029</v>
+        <v>8.3671299227559</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         </is>
       </c>
       <c r="E169">
-        <v>86.23974592228819</v>
+        <v>82.88359142759428</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         </is>
       </c>
       <c r="E170">
-        <v>14.33773485520216</v>
+        <v>13.80929399800245</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         </is>
       </c>
       <c r="E171">
-        <v>75.8419838645945</v>
+        <v>73.48053411902019</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -5166,7 +5166,7 @@
         </is>
       </c>
       <c r="E172">
-        <v>155.5258841066533</v>
+        <v>150.5533077607931</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         </is>
       </c>
       <c r="E173">
-        <v>14.71475417865928</v>
+        <v>14.23533900358492</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         </is>
       </c>
       <c r="E174">
-        <v>7.707303846878894</v>
+        <v>7.459648078538013</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         </is>
       </c>
       <c r="E175">
-        <v>74.90149537607689</v>
+        <v>72.1908611376339</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -5278,7 +5278,7 @@
         </is>
       </c>
       <c r="E176">
-        <v>13.0088770882371</v>
+        <v>12.50000074088168</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -5306,7 +5306,7 @@
         </is>
       </c>
       <c r="E177">
-        <v>78.62031330602049</v>
+        <v>76.24772791302443</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         </is>
       </c>
       <c r="E178">
-        <v>157.6607690378383</v>
+        <v>152.7075076279922</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="E179">
-        <v>14.71750284660536</v>
+        <v>14.24224219187603</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="E180">
-        <v>6.934707846572935</v>
+        <v>6.698689503575426</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -5418,7 +5418,7 @@
         </is>
       </c>
       <c r="E181">
-        <v>67.84973503965287</v>
+        <v>65.2437320291361</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
         </is>
       </c>
       <c r="E182">
-        <v>22.10646593965314</v>
+        <v>21.54654578575667</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -5474,7 +5474,7 @@
         </is>
       </c>
       <c r="E183">
-        <v>122.6403701499406</v>
+        <v>120.202761606125</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -5502,7 +5502,7 @@
         </is>
       </c>
       <c r="E184">
-        <v>249.9024696228114</v>
+        <v>244.7467526711368</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         </is>
       </c>
       <c r="E185">
-        <v>23.52637116237373</v>
+        <v>23.02776894330781</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         </is>
       </c>
       <c r="E186">
-        <v>12.1524194538808</v>
+        <v>11.8954272221248</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         </is>
       </c>
       <c r="E187">
-        <v>116.5339536270489</v>
+        <v>113.6695564498351</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -5614,7 +5614,7 @@
         </is>
       </c>
       <c r="E188">
-        <v>19.6871203455039</v>
+        <v>19.1417617160104</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -5642,7 +5642,7 @@
         </is>
       </c>
       <c r="E189">
-        <v>126.8567397473145</v>
+        <v>124.4086490724346</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -5670,7 +5670,7 @@
         </is>
       </c>
       <c r="E190">
-        <v>252.3263484161272</v>
+        <v>247.1818437166733</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -5698,7 +5698,7 @@
         </is>
       </c>
       <c r="E191">
-        <v>23.41009720909171</v>
+        <v>22.91433184991129</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         </is>
       </c>
       <c r="E192">
-        <v>10.74222519827675</v>
+        <v>10.49402149084992</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="E193">
-        <v>103.5991534395858</v>
+        <v>100.8139995841473</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         </is>
       </c>
       <c r="E194">
-        <v>17.06914442023254</v>
+        <v>16.67392722682076</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
         </is>
       </c>
       <c r="E195">
-        <v>91.02243193037398</v>
+        <v>89.27147778379366</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         </is>
       </c>
       <c r="E196">
-        <v>186.8229183905125</v>
+        <v>183.1274168923798</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         </is>
       </c>
       <c r="E197">
-        <v>17.65900482396506</v>
+        <v>17.30237265235373</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         </is>
       </c>
       <c r="E198">
-        <v>9.500479062096645</v>
+        <v>9.314451858916145</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -5922,7 +5922,7 @@
         </is>
       </c>
       <c r="E199">
-        <v>90.13734005409788</v>
+        <v>88.10475546037877</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         </is>
       </c>
       <c r="E200">
-        <v>15.06909049599875</v>
+        <v>14.69009395693359</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         </is>
       </c>
       <c r="E201">
-        <v>94.98143134248156</v>
+        <v>93.22016610145512</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         </is>
       </c>
       <c r="E202">
-        <v>189.6172191032674</v>
+        <v>185.9363792484872</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         </is>
       </c>
       <c r="E203">
-        <v>17.62807149510867</v>
+        <v>17.27477691568245</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         </is>
       </c>
       <c r="E204">
-        <v>8.328725436442184</v>
+        <v>8.152515404478487</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -6090,7 +6090,7 @@
         </is>
       </c>
       <c r="E205">
-        <v>79.41926680298648</v>
+        <v>77.47458026654135</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         </is>
       </c>
       <c r="E206">
-        <v>26.78876453333154</v>
+        <v>26.36721728788661</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
         </is>
       </c>
       <c r="E207">
-        <v>148.3195183149001</v>
+        <v>146.499016406456</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -6174,7 +6174,7 @@
         </is>
       </c>
       <c r="E208">
-        <v>303.009426349719</v>
+        <v>299.1507722046787</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -6202,7 +6202,7 @@
         </is>
       </c>
       <c r="E209">
-        <v>28.52938515115283</v>
+        <v>28.15587849686433</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -6230,7 +6230,7 @@
         </is>
       </c>
       <c r="E210">
-        <v>15.18823783124692</v>
+        <v>14.99394632528867</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -6258,7 +6258,7 @@
         </is>
       </c>
       <c r="E211">
-        <v>142.7677167793263</v>
+        <v>140.6065025730524</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         </is>
       </c>
       <c r="E212">
-        <v>23.21282279786247</v>
+        <v>22.80387603324827</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -6314,7 +6314,7 @@
         </is>
       </c>
       <c r="E213">
-        <v>154.3991091610429</v>
+        <v>152.5680482337391</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         </is>
       </c>
       <c r="E214">
-        <v>306.2629020420168</v>
+        <v>302.4117799245637</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
         </is>
       </c>
       <c r="E215">
-        <v>28.3295584670153</v>
+        <v>27.95833110055958</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         </is>
       </c>
       <c r="E216">
-        <v>13.08592179166523</v>
+        <v>12.89932757147781</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -6426,7 +6426,7 @@
         </is>
       </c>
       <c r="E217">
-        <v>123.4736623003362</v>
+        <v>121.3818821144211</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -6454,7 +6454,7 @@
         </is>
       </c>
       <c r="E218">
-        <v>20.08858710433837</v>
+        <v>19.81051931031979</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -6482,7 +6482,7 @@
         </is>
       </c>
       <c r="E219">
-        <v>107.7006099945365</v>
+        <v>106.4773184023168</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         </is>
       </c>
       <c r="E220">
-        <v>221.4507011309548</v>
+        <v>218.863226993092</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -6538,7 +6538,7 @@
         </is>
       </c>
       <c r="E221">
-        <v>20.91880670328597</v>
+        <v>20.66890783850622</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         </is>
       </c>
       <c r="E222">
-        <v>11.49234711814108</v>
+        <v>11.36095306275452</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -6594,7 +6594,7 @@
         </is>
       </c>
       <c r="E223">
-        <v>107.506903859628</v>
+        <v>106.0717975549646</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="E224">
-        <v>17.26169338853559</v>
+        <v>16.99624879618826</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         </is>
       </c>
       <c r="E225">
-        <v>113.0822690235323</v>
+        <v>111.8496855470843</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         </is>
       </c>
       <c r="E226">
-        <v>224.9698134328798</v>
+        <v>222.3920138691782</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         </is>
       </c>
       <c r="E227">
-        <v>20.83876675674163</v>
+        <v>20.59132640751653</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         </is>
       </c>
       <c r="E228">
-        <v>9.823362273123589</v>
+        <v>9.69970525540896</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         </is>
       </c>
       <c r="E229">
-        <v>92.1873036237961</v>
+        <v>90.82162041977708</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         </is>
       </c>
       <c r="E230">
-        <v>32.19883289235085</v>
+        <v>31.89923255878114</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         </is>
       </c>
       <c r="E231">
-        <v>177.5095373482262</v>
+        <v>176.2222331633511</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         </is>
       </c>
       <c r="E232">
-        <v>363.8464443075751</v>
+        <v>361.1129040335671</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         </is>
       </c>
       <c r="E233">
-        <v>34.2704444555524</v>
+        <v>34.00569712111855</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         </is>
       </c>
       <c r="E234">
-        <v>18.68977821958627</v>
+        <v>18.55073597819438</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="E235">
-        <v>173.8315493368013</v>
+        <v>172.2901712543547</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -6958,7 +6958,7 @@
         </is>
       </c>
       <c r="E236">
-        <v>27.17540498325462</v>
+        <v>26.88653771121504</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         </is>
       </c>
       <c r="E237">
-        <v>185.91377913758</v>
+        <v>184.6158441679638</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="E238">
-        <v>368.0712045569608</v>
+        <v>365.3416093262207</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -7042,7 +7042,7 @@
         </is>
       </c>
       <c r="E239">
-        <v>33.95988867140836</v>
+        <v>33.69688216939077</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         </is>
       </c>
       <c r="E240">
-        <v>15.71288088141712</v>
+        <v>15.5804387966478</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         </is>
       </c>
       <c r="E241">
-        <v>146.4402418356422</v>
+        <v>144.9587641840179</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         </is>
       </c>
       <c r="E242">
-        <v>23.40694022998734</v>
+        <v>23.21193629878864</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -7154,7 +7154,7 @@
         </is>
       </c>
       <c r="E243">
-        <v>125.8848168438423</v>
+        <v>125.0308619121589</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         </is>
       </c>
       <c r="E244">
-        <v>259.4124286475496</v>
+        <v>257.602691695865</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         </is>
       </c>
       <c r="E245">
-        <v>24.49555626014267</v>
+        <v>24.32068527659289</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -7238,7 +7238,7 @@
         </is>
       </c>
       <c r="E246">
-        <v>13.66873485383145</v>
+        <v>13.57599448040668</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
         </is>
       </c>
       <c r="E247">
-        <v>126.9947538154113</v>
+        <v>125.9838885999124</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -7294,7 +7294,7 @@
         </is>
       </c>
       <c r="E248">
-        <v>19.60145284076007</v>
+        <v>19.41654942351269</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         </is>
       </c>
       <c r="E249">
-        <v>132.9259762340672</v>
+        <v>132.0631642623497</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -7350,7 +7350,7 @@
         </is>
       </c>
       <c r="E250">
-        <v>263.7139070137221</v>
+        <v>261.9098174777049</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -7378,7 +7378,7 @@
         </is>
       </c>
       <c r="E251">
-        <v>24.35077063890406</v>
+        <v>24.17769748807103</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         </is>
       </c>
       <c r="E252">
-        <v>11.40514080259567</v>
+        <v>11.31863946518081</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -7434,7 +7434,7 @@
         </is>
       </c>
       <c r="E253">
-        <v>106.1425061547482</v>
+        <v>105.1879808989851</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="E254">
-        <v>38.36729576794439</v>
+        <v>38.15364282689659</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         </is>
       </c>
       <c r="E255">
-        <v>210.3273866315178</v>
+        <v>209.4105133533063</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         </is>
       </c>
       <c r="E256">
-        <v>432.6388607909485</v>
+        <v>430.6888901269341</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -7546,7 +7546,7 @@
         </is>
       </c>
       <c r="E257">
-        <v>40.77185806827607</v>
+        <v>40.58298428743964</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -7574,7 +7574,7 @@
         </is>
       </c>
       <c r="E258">
-        <v>22.65604816984502</v>
+        <v>22.55559352304947</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         </is>
       </c>
       <c r="E259">
-        <v>209.8142845182396</v>
+        <v>208.7090764766753</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -7630,7 +7630,7 @@
         </is>
       </c>
       <c r="E260">
-        <v>31.58879584441754</v>
+        <v>31.38497927526932</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
         </is>
       </c>
       <c r="E261">
-        <v>221.5479573198888</v>
+        <v>220.6196872711895</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -7686,7 +7686,7 @@
         </is>
       </c>
       <c r="E262">
-        <v>437.982570946968</v>
+        <v>436.0336547811688</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="E263">
-        <v>40.32156304411649</v>
+        <v>40.13407596090691</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -7742,7 +7742,7 @@
         </is>
       </c>
       <c r="E264">
-        <v>18.60950358100557</v>
+        <v>18.5151143591118</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         </is>
       </c>
       <c r="E265">
-        <v>172.4668058640005</v>
+        <v>171.4171058125426</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         </is>
       </c>
       <c r="E266">
-        <v>27.05283799569401</v>
+        <v>26.90954132639232</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -7826,7 +7826,7 @@
         </is>
       </c>
       <c r="E267">
-        <v>145.7394081368024</v>
+        <v>145.1123566689846</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -7854,7 +7854,7 @@
         </is>
       </c>
       <c r="E268">
-        <v>301.0400088135876</v>
+        <v>299.7089163967192</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         </is>
       </c>
       <c r="E269">
-        <v>28.42042162655739</v>
+        <v>28.29179734327085</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         </is>
       </c>
       <c r="E270">
-        <v>16.03801874852506</v>
+        <v>15.96900353441146</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -7938,7 +7938,7 @@
         </is>
       </c>
       <c r="E271">
-        <v>148.7535292411307</v>
+        <v>148.0058411998093</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
         </is>
       </c>
       <c r="E272">
-        <v>22.0996287890783</v>
+        <v>21.96533399741799</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         </is>
       </c>
       <c r="E273">
-        <v>154.7121327505273</v>
+        <v>154.0756429673368</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         </is>
       </c>
       <c r="E274">
-        <v>306.1952630864097</v>
+        <v>304.8668442105301</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         </is>
       </c>
       <c r="E275">
-        <v>28.19397773562938</v>
+        <v>28.06676385734236</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         </is>
       </c>
       <c r="E276">
-        <v>13.07160854659603</v>
+        <v>13.00817291761372</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -8106,7 +8106,7 @@
         </is>
       </c>
       <c r="E277">
-        <v>121.3138482445527</v>
+        <v>120.6170247190039</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -8134,7 +8134,7 @@
         </is>
       </c>
       <c r="E278">
-        <v>45.37354907150414</v>
+        <v>45.21210016495336</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="E279">
-        <v>247.2305887268474</v>
+        <v>246.53493391808</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         </is>
       </c>
       <c r="E280">
-        <v>510.3418826799908</v>
+        <v>508.8603789038742</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -8218,7 +8218,7 @@
         </is>
       </c>
       <c r="E281">
-        <v>48.12324069095544</v>
+        <v>47.97982448114595</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -8246,7 +8246,7 @@
         </is>
       </c>
       <c r="E282">
-        <v>27.12828069659215</v>
+        <v>27.05061201097141</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
         </is>
       </c>
       <c r="E283">
-        <v>251.2121430875818</v>
+        <v>250.3693577540839</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="E284">
-        <v>36.48006060601188</v>
+        <v>36.32888409860399</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -8330,7 +8330,7 @@
         </is>
       </c>
       <c r="E285">
-        <v>261.8529464946929</v>
+        <v>261.1438264996326</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         </is>
       </c>
       <c r="E286">
-        <v>516.9846044549046</v>
+        <v>515.5017755736967</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -8386,7 +8386,7 @@
         </is>
       </c>
       <c r="E287">
-        <v>47.49973348807715</v>
+        <v>47.35756768536165</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         </is>
       </c>
       <c r="E288">
-        <v>21.78448392204842</v>
+        <v>21.71315698622234</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
         </is>
       </c>
       <c r="E289">
-        <v>201.7071460775655</v>
+        <v>200.922895565677</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -8470,7 +8470,7 @@
         </is>
       </c>
       <c r="E290">
-        <v>30.73041371420532</v>
+        <v>30.61790489031454</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         </is>
       </c>
       <c r="E291">
-        <v>165.9324606701379</v>
+        <v>165.4376145300425</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         </is>
       </c>
       <c r="E292">
-        <v>343.4770399110614</v>
+        <v>342.4251812007815</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
         </is>
       </c>
       <c r="E293">
-        <v>32.41843042634166</v>
+        <v>32.31685856418951</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -8582,7 +8582,7 @@
         </is>
       </c>
       <c r="E294">
-        <v>18.43305440324782</v>
+        <v>18.37762415541032</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         </is>
       </c>
       <c r="E295">
-        <v>171.1328663644242</v>
+        <v>170.5398965244905</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -8638,7 +8638,7 @@
         </is>
       </c>
       <c r="E296">
-        <v>24.51457816154652</v>
+        <v>24.41123053389992</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         </is>
       </c>
       <c r="E297">
-        <v>177.0355832954939</v>
+        <v>176.5295956387437</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         </is>
       </c>
       <c r="E298">
-        <v>349.5344250148884</v>
+        <v>348.4829111357031</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -8722,7 +8722,7 @@
         </is>
       </c>
       <c r="E299">
-        <v>32.0985524317897</v>
+        <v>31.99822238981042</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -8750,7 +8750,7 @@
         </is>
       </c>
       <c r="E300">
-        <v>14.68591657180135</v>
+        <v>14.6361724927646</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -8778,7 +8778,7 @@
         </is>
       </c>
       <c r="E301">
-        <v>136.3292150432774</v>
+        <v>135.7885878242447</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -8806,7 +8806,7 @@
         </is>
       </c>
       <c r="E302">
-        <v>52.78990571678842</v>
+        <v>52.65747897696327</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         </is>
       </c>
       <c r="E303">
-        <v>286.4028943391754</v>
+        <v>285.826157154153</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -8862,7 +8862,7 @@
         </is>
       </c>
       <c r="E304">
-        <v>593.0370908782518</v>
+        <v>591.8073688775074</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -8890,7 +8890,7 @@
         </is>
       </c>
       <c r="E305">
-        <v>55.94479738357402</v>
+        <v>55.82592058255982</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         </is>
       </c>
       <c r="E306">
-        <v>31.87069110423831</v>
+        <v>31.80470237205228</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -8946,7 +8946,7 @@
         </is>
       </c>
       <c r="E307">
-        <v>295.7040150205262</v>
+        <v>295.0029528899628</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         </is>
       </c>
       <c r="E308">
-        <v>41.48737212104258</v>
+        <v>41.36701970922696</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -9002,7 +9002,7 @@
         </is>
       </c>
       <c r="E309">
-        <v>304.9281029966129</v>
+        <v>304.3341991615636</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -9030,7 +9030,7 @@
         </is>
       </c>
       <c r="E310">
-        <v>601.1294056056789</v>
+        <v>599.8960878295801</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         </is>
       </c>
       <c r="E311">
-        <v>55.12061992787471</v>
+        <v>55.0030472660949</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -9086,7 +9086,7 @@
         </is>
       </c>
       <c r="E312">
-        <v>25.0367122524369</v>
+        <v>24.9781905905395</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         </is>
       </c>
       <c r="E313">
-        <v>232.1552690226975</v>
+        <v>231.5235978008365</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -9142,7 +9142,7 @@
         </is>
       </c>
       <c r="E314">
-        <v>34.28969145096269</v>
+        <v>34.19508610420606</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="E315">
-        <v>185.8427129126939</v>
+        <v>185.4213821508405</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         </is>
       </c>
       <c r="E316">
-        <v>385.3659545542479</v>
+        <v>384.4693700761371</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         </is>
       </c>
       <c r="E317">
-        <v>36.35759029249135</v>
+        <v>36.27114902042658</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -9254,7 +9254,7 @@
         </is>
       </c>
       <c r="E318">
-        <v>20.78077708124486</v>
+        <v>20.73248474826204</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -9282,7 +9282,7 @@
         </is>
       </c>
       <c r="E319">
-        <v>193.2877837951818</v>
+        <v>192.7814576496655</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         </is>
       </c>
       <c r="E320">
-        <v>26.7338819095612</v>
+        <v>26.6497253505586</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -9338,7 +9338,7 @@
         </is>
       </c>
       <c r="E321">
-        <v>199.2240454462132</v>
+        <v>198.7885664225433</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -9366,7 +9366,7 @@
         </is>
       </c>
       <c r="E322">
-        <v>392.3564345878357</v>
+        <v>391.4580403773811</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -9394,7 +9394,7 @@
         </is>
       </c>
       <c r="E323">
-        <v>35.93594564199842</v>
+        <v>35.85074157563709</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -9422,7 +9422,7 @@
         </is>
       </c>
       <c r="E324">
-        <v>16.19365445833161</v>
+        <v>16.15186209307122</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -9450,7 +9450,7 @@
         </is>
       </c>
       <c r="E325">
-        <v>150.535242045229</v>
+        <v>150.0892197158021</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         </is>
       </c>
       <c r="E326">
-        <v>60.35063840780064</v>
+        <v>60.23203310731741</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         </is>
       </c>
       <c r="E327">
-        <v>326.8171581133763</v>
+        <v>326.2912227220903</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -9534,7 +9534,7 @@
         </is>
       </c>
       <c r="E328">
-        <v>678.4724250173784</v>
+        <v>677.3497688609218</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         </is>
       </c>
       <c r="E329">
-        <v>64.01565952081363</v>
+        <v>63.90737899093148</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -9590,7 +9590,7 @@
         </is>
       </c>
       <c r="E330">
-        <v>36.75692183671068</v>
+        <v>36.69495445932462</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
         </is>
       </c>
       <c r="E331">
-        <v>341.8656781495823</v>
+        <v>341.2250738511784</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -9646,7 +9646,7 @@
         </is>
       </c>
       <c r="E332">
-        <v>46.39865994996264</v>
+        <v>46.2954672792733</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         </is>
       </c>
       <c r="E333">
-        <v>349.6795663460305</v>
+        <v>349.1305868802515</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -9702,7 +9702,7 @@
         </is>
       </c>
       <c r="E334">
-        <v>688.1413610677307</v>
+        <v>687.0124984473605</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         </is>
       </c>
       <c r="E335">
-        <v>62.96828172963524</v>
+        <v>62.86153585283042</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -9758,7 +9758,7 @@
         </is>
       </c>
       <c r="E336">
-        <v>28.26374665253589</v>
+        <v>28.21134860014805</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
         </is>
       </c>
       <c r="E337">
-        <v>262.6382618544806</v>
+        <v>262.0869894751667</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -9814,7 +9814,7 @@
         </is>
       </c>
       <c r="E338">
-        <v>37.59896851641613</v>
+        <v>37.51333791078965</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         </is>
       </c>
       <c r="E339">
-        <v>205.014775234656</v>
+        <v>204.6256806563889</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -9870,7 +9870,7 @@
         </is>
       </c>
       <c r="E340">
-        <v>425.6707749643555</v>
+        <v>424.8420493269687</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         </is>
       </c>
       <c r="E341">
-        <v>40.13491104015412</v>
+        <v>40.0552088621867</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         </is>
       </c>
       <c r="E342">
-        <v>23.01891537803209</v>
+        <v>22.9730993458891</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -9954,7 +9954,7 @@
         </is>
       </c>
       <c r="E343">
-        <v>214.4839644548425</v>
+        <v>214.0159415055474</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         </is>
       </c>
       <c r="E344">
-        <v>28.68006512287053</v>
+        <v>28.60726332849945</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -10010,7 +10010,7 @@
         </is>
       </c>
       <c r="E345">
-        <v>220.7448789389918</v>
+        <v>220.3371566912826</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -10038,7 +10038,7 @@
         </is>
       </c>
       <c r="E346">
-        <v>433.5980411850986</v>
+        <v>432.765239641462</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
         </is>
       </c>
       <c r="E347">
-        <v>39.60800311255709</v>
+        <v>39.52966999320715</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -10094,7 +10094,7 @@
         </is>
       </c>
       <c r="E348">
-        <v>17.56065630867753</v>
+        <v>17.52285444924858</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -10122,7 +10122,7 @@
         </is>
       </c>
       <c r="E349">
-        <v>163.4838549539269</v>
+        <v>163.0905641898568</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -10150,7 +10150,7 @@
         </is>
       </c>
       <c r="E350">
-        <v>67.60844373803708</v>
+        <v>67.49246266208971</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -10178,7 +10178,7 @@
         </is>
       </c>
       <c r="E351">
-        <v>366.7617420716389</v>
+        <v>366.235105152303</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         </is>
       </c>
       <c r="E352">
-        <v>762.8582400258048</v>
+        <v>761.7330355562151</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -10234,7 +10234,7 @@
         </is>
       </c>
       <c r="E353">
-        <v>71.9639160259127</v>
+        <v>71.85570442419112</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -10262,7 +10262,7 @@
         </is>
       </c>
       <c r="E354">
-        <v>41.54986252089515</v>
+        <v>41.48594145190719</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -10290,7 +10290,7 @@
         </is>
       </c>
       <c r="E355">
-        <v>387.2382396806774</v>
+        <v>386.5963981136998</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
         </is>
       </c>
       <c r="E356">
-        <v>50.90972996996644</v>
+        <v>50.81414047571432</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -10346,7 +10346,7 @@
         </is>
       </c>
       <c r="E357">
-        <v>394.1901606789565</v>
+        <v>393.6320958311004</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -10374,7 +10374,7 @@
         </is>
       </c>
       <c r="E358">
-        <v>774.1584387441278</v>
+        <v>773.0238275126553</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -10402,7 +10402,7 @@
         </is>
       </c>
       <c r="E359">
-        <v>70.6835489352713</v>
+        <v>70.577273482499</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         </is>
       </c>
       <c r="E360">
-        <v>31.30539718465364</v>
+        <v>31.2542107016705</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -10458,7 +10458,7 @@
         </is>
       </c>
       <c r="E361">
-        <v>291.4574125789755</v>
+        <v>290.9347508691256</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
         </is>
       </c>
       <c r="E362">
-        <v>40.55841414782792</v>
+        <v>40.4760629027523</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -10514,7 +10514,7 @@
         </is>
       </c>
       <c r="E363">
-        <v>223.1454578235995</v>
+        <v>222.7620062474014</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         </is>
       </c>
       <c r="E364">
-        <v>463.6808004947094</v>
+        <v>462.8636246531863</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -10570,7 +10570,7 @@
         </is>
       </c>
       <c r="E365">
-        <v>43.678537817886</v>
+        <v>43.6001755128119</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -10598,7 +10598,7 @@
         </is>
       </c>
       <c r="E366">
-        <v>25.09954890168855</v>
+        <v>25.05325139912158</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         </is>
       </c>
       <c r="E367">
-        <v>234.1743443568069</v>
+        <v>233.7135176200886</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -10654,7 +10654,7 @@
         </is>
       </c>
       <c r="E368">
-        <v>30.30764581434546</v>
+        <v>30.24114416522532</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         </is>
       </c>
       <c r="E369">
-        <v>241.2161608406293</v>
+        <v>240.8087141046565</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         </is>
       </c>
       <c r="E370">
-        <v>472.5202262628738</v>
+        <v>471.696699122499</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         </is>
       </c>
       <c r="E371">
-        <v>43.04764793409925</v>
+        <v>42.97087228033804</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -10766,7 +10766,7 @@
         </is>
       </c>
       <c r="E372">
-        <v>18.76784914797185</v>
+        <v>18.7315181927026</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -10794,7 +10794,7 @@
         </is>
       </c>
       <c r="E373">
-        <v>174.9177450337698</v>
+        <v>174.5501116152308</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -10822,7 +10822,7 @@
         </is>
       </c>
       <c r="E374">
-        <v>74.27783960609271</v>
+        <v>74.15759033239154</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         </is>
       </c>
       <c r="E375">
-        <v>405.2524012328207</v>
+        <v>404.6925037995029</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="E376">
-        <v>843.9655108328603</v>
+        <v>842.7685873168311</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         </is>
       </c>
       <c r="E377">
-        <v>79.56793069236093</v>
+        <v>79.45316496458507</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -10934,7 +10934,7 @@
         </is>
       </c>
       <c r="E378">
-        <v>46.1008768694003</v>
+        <v>46.03131189986697</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -10962,7 +10962,7 @@
         </is>
       </c>
       <c r="E379">
-        <v>430.2679280498261</v>
+        <v>429.5862443467277</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -10990,7 +10990,7 @@
         </is>
       </c>
       <c r="E380">
-        <v>54.85558343733076</v>
+        <v>54.76166178919819</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -11018,7 +11018,7 @@
         </is>
       </c>
       <c r="E381">
-        <v>437.3041105027752</v>
+        <v>436.7028476848758</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         </is>
       </c>
       <c r="E382">
-        <v>856.8931360658264</v>
+        <v>855.6832759222947</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -11074,7 +11074,7 @@
         </is>
       </c>
       <c r="E383">
-        <v>78.05571748133062</v>
+        <v>77.94339215496232</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         </is>
       </c>
       <c r="E384">
-        <v>34.07768416093532</v>
+        <v>34.02468627335387</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -11130,7 +11130,7 @@
         </is>
       </c>
       <c r="E385">
-        <v>317.6988084871076</v>
+        <v>317.1723480064787</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
